--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:53:46+00:00</t>
+    <t>2026-08-27T20:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T20:51:52+00:00</t>
+    <t>2026-08-28T05:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:43:02+00:00</t>
+    <t>2026-08-28T09:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
